--- a/data/trans_dic/P64D$otros_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,55</t>
+          <t>0,37; 1,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,15</t>
+          <t>0,2; 1,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,11</t>
+          <t>0,36; 1,13</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,52</t>
+          <t>0,3; 2,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,55</t>
+          <t>0,29; 2,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,01</t>
+          <t>0,39; 2,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,44</t>
+          <t>0,46; 1,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,12</t>
+          <t>0,3; 1,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,13</t>
+          <t>0,48; 1,19</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5849</t>
+          <t>0; 6229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1264</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5365</t>
+          <t>0; 6271</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4733; 21410</t>
+          <t>5081; 21558</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1814; 10899</t>
+          <t>1877; 10043</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8765; 25866</t>
+          <t>8471; 26363</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1383; 11279</t>
+          <t>1360; 10981</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1305; 11121</t>
+          <t>1283; 10560</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3440; 17709</t>
+          <t>3453; 17628</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9218; 28192</t>
+          <t>8927; 28001</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4426; 16393</t>
+          <t>4376; 17835</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16608; 38577</t>
+          <t>16541; 40725</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$otros_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Estudios-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,56</t>
+          <t>0,55; 1,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,06</t>
+          <t>0,37; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,13</t>
+          <t>0,59; 1,48</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,46</t>
+          <t>0,54; 3,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,43</t>
+          <t>0,29; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,0</t>
+          <t>0,56; 2,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,43</t>
+          <t>0,67; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,22</t>
+          <t>0,46; 1,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,19</t>
+          <t>0,7; 1,45</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>2045</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6229</t>
+          <t>0; 6554</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6271</t>
+          <t>0; 7364</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>21294</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5081; 21558</t>
+          <t>6946; 23115</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1877; 10043</t>
+          <t>3529; 17923</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8471; 26363</t>
+          <t>13080; 32897</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>11045</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1360; 10981</t>
+          <t>2653; 15059</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1283; 10560</t>
+          <t>1372; 10933</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3453; 17628</t>
+          <t>5443; 20302</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25791</t>
+          <t>34384</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8927; 28001</t>
+          <t>12920; 34186</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4376; 17835</t>
+          <t>6992; 24819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16541; 40725</t>
+          <t>24038; 49860</t>
         </is>
       </c>
     </row>
